--- a/brand-protection/2026-09-28/strike/07-mono_hidden.xlsx
+++ b/brand-protection/2026-09-28/strike/07-mono_hidden.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B121"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,11 @@
           <t>Tags</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +444,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,6 +461,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -463,6 +478,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -475,6 +495,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -487,6 +512,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -499,6 +529,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -511,6 +546,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -523,6 +563,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -535,6 +580,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -547,6 +597,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -559,6 +614,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -571,6 +631,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -583,6 +648,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -595,6 +665,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -607,6 +682,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -619,6 +699,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -631,6 +716,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -643,6 +733,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -655,6 +750,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -667,6 +767,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -679,6 +784,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -691,6 +801,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -703,6 +818,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -715,6 +835,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -727,6 +852,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -739,6 +869,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -751,6 +886,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -763,6 +903,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -775,6 +920,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -787,6 +937,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -799,6 +954,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -811,6 +971,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -823,6 +988,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -835,6 +1005,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -847,6 +1022,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -859,6 +1039,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -871,6 +1056,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -883,6 +1073,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -895,6 +1090,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -907,6 +1107,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -919,6 +1124,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -931,6 +1141,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -943,6 +1158,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -955,6 +1175,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -967,6 +1192,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -979,6 +1209,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -991,6 +1226,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1003,6 +1243,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1015,6 +1260,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1027,6 +1277,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1039,6 +1294,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1051,6 +1311,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1063,6 +1328,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1075,6 +1345,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1087,6 +1362,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1099,6 +1379,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1111,6 +1396,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1123,6 +1413,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1135,6 +1430,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1147,6 +1447,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1159,6 +1464,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1171,6 +1481,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1183,6 +1498,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1195,6 +1515,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1207,6 +1532,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1219,6 +1549,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1231,6 +1566,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1243,6 +1583,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1255,6 +1600,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1267,6 +1617,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1279,6 +1634,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1291,6 +1651,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1303,6 +1668,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1315,6 +1685,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1327,6 +1702,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1339,6 +1719,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1351,6 +1736,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1363,6 +1753,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1375,6 +1770,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1387,6 +1787,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1399,6 +1804,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1411,6 +1821,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1423,6 +1838,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1435,6 +1855,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1447,6 +1872,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1459,6 +1889,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1471,6 +1906,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1483,6 +1923,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1495,6 +1940,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1507,6 +1957,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1519,6 +1974,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1531,6 +1991,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1543,6 +2008,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1555,6 +2025,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1567,6 +2042,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1579,6 +2059,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1591,6 +2076,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1603,6 +2093,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1615,6 +2110,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1627,6 +2127,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1639,6 +2144,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1651,6 +2161,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1663,6 +2178,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1675,6 +2195,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1687,6 +2212,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1699,6 +2229,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1711,6 +2246,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1723,6 +2263,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1735,6 +2280,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1747,6 +2297,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1759,6 +2314,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1771,6 +2331,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1783,6 +2348,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1795,6 +2365,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1807,6 +2382,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1819,6 +2399,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1831,6 +2416,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1843,6 +2433,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1855,6 +2450,11 @@
           <t>strike-07-mono-hidden</t>
         </is>
       </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1865,6 +2465,11 @@
       <c r="B121" t="inlineStr">
         <is>
           <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Trademark Infringement</t>
         </is>
       </c>
     </row>

--- a/brand-protection/2026-09-28/strike/07-mono_hidden.xlsx
+++ b/brand-protection/2026-09-28/strike/07-mono_hidden.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="sample" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,23 +413,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>url</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>label</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>website_category</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>phone_number</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>email_address</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>whatsapp</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>wechat</t>
         </is>
       </c>
     </row>
@@ -441,12 +491,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>mostbet10646.company</t>
         </is>
       </c>
     </row>
@@ -458,12 +513,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>mostbet12044.ru</t>
         </is>
       </c>
     </row>
@@ -475,12 +540,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>mostbet12045.ru</t>
         </is>
       </c>
     </row>
@@ -492,12 +567,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>mostbet12046.ru</t>
         </is>
       </c>
     </row>
@@ -509,12 +594,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>mostbet12047.ru</t>
         </is>
       </c>
     </row>
@@ -526,12 +621,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mostbet12048.ru</t>
         </is>
       </c>
     </row>
@@ -543,12 +648,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>mostbet12049.ru</t>
         </is>
       </c>
     </row>
@@ -560,12 +675,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>mostbet13374.help</t>
         </is>
       </c>
     </row>
@@ -577,12 +697,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>mostbet14473.help</t>
         </is>
       </c>
     </row>
@@ -594,12 +719,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>mostbet15247.help</t>
         </is>
       </c>
     </row>
@@ -611,12 +741,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>mostbet15743.help</t>
         </is>
       </c>
     </row>
@@ -628,12 +763,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>mostbet18178.company</t>
         </is>
       </c>
     </row>
@@ -645,12 +785,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>mostbet18247.help</t>
         </is>
       </c>
     </row>
@@ -662,12 +807,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>mostbet18715.company</t>
         </is>
       </c>
     </row>
@@ -679,12 +829,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>mostbet19142.shop</t>
         </is>
       </c>
     </row>
@@ -696,12 +851,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>mostbet20010.shop</t>
         </is>
       </c>
     </row>
@@ -713,12 +873,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>mostbet2027.help</t>
         </is>
       </c>
     </row>
@@ -730,12 +895,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>mostbet2028.help</t>
         </is>
       </c>
     </row>
@@ -747,12 +917,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>mostbet2029.help</t>
         </is>
       </c>
     </row>
@@ -764,12 +939,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>mostbet2030.help</t>
         </is>
       </c>
     </row>
@@ -781,12 +961,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>mostbet2031.help</t>
         </is>
       </c>
     </row>
@@ -798,12 +983,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>mostbet2032.help</t>
         </is>
       </c>
     </row>
@@ -815,12 +1005,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>mostbet2033.help</t>
         </is>
       </c>
     </row>
@@ -832,12 +1027,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>mostbet2034.help</t>
         </is>
       </c>
     </row>
@@ -849,12 +1049,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>mostbet2035.help</t>
         </is>
       </c>
     </row>
@@ -866,12 +1071,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>mostbet20553.shop</t>
         </is>
       </c>
     </row>
@@ -883,12 +1093,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>mostbet2062.help</t>
         </is>
       </c>
     </row>
@@ -900,12 +1115,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>mostbet2063.help</t>
         </is>
       </c>
     </row>
@@ -917,12 +1137,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>mostbet2064.help</t>
         </is>
       </c>
     </row>
@@ -934,12 +1159,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>mostbet2065.help</t>
         </is>
       </c>
     </row>
@@ -951,12 +1181,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>mostbet2066.help</t>
         </is>
       </c>
     </row>
@@ -968,12 +1203,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>mostbet2067.help</t>
         </is>
       </c>
     </row>
@@ -985,12 +1225,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>mostbet2068.help</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1247,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>mostbet2069.help</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1269,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>mostbet2070.help</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1291,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>mostbet21480.help</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1313,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>mostbet21611.icu</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1335,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>mostbet22685.online</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1357,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>mostbet26809.help</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1379,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>mostbet28470.help</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1401,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>mostbet28648.help</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1423,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>mostbet30760.company</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1445,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>mostbet31422.icu</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1467,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>mostbet33270.company</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1489,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>mostbet33465.online</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1511,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>mostbet3347.help</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1533,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>mostbet33907.online</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1555,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>mostbet34192.company</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1577,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>mostbet35849.help</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1599,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>mostbet37461.help</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1621,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>mostbet38201.online</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1643,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>mostbet39081.help</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1665,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>mostbet39930.help</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1687,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>mostbet40483.help</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1709,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>mostbet41248.help</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1731,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>mostbet41254.help</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1753,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>mostbet42299.help</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1775,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>mostbet42395.help</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1797,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>mostbet42718.help</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1819,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>mostbet44719.online</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1841,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>mostbet4478.shop</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1863,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>mostbet45177.help</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1885,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>mostbet46402.online</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1907,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>mostbet47045.online</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1929,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>mostbet47272.online</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1951,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>mostbet47394.company</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1973,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>mostbet49271.help</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1995,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>mostbet49581.online</t>
         </is>
       </c>
     </row>
@@ -1597,12 +2017,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>mostbet49791.online</t>
         </is>
       </c>
     </row>
@@ -1614,12 +2039,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>mostbet49882.help</t>
         </is>
       </c>
     </row>
@@ -1631,12 +2061,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>mostbet50122.icu</t>
         </is>
       </c>
     </row>
@@ -1648,12 +2083,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>mostbet5059.help</t>
         </is>
       </c>
     </row>
@@ -1665,12 +2105,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>mostbet51338.help</t>
         </is>
       </c>
     </row>
@@ -1682,12 +2127,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>mostbet51837.help</t>
         </is>
       </c>
     </row>
@@ -1699,12 +2149,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>mostbet52613.shop</t>
         </is>
       </c>
     </row>
@@ -1716,12 +2171,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>mostbet52813.online</t>
         </is>
       </c>
     </row>
@@ -1733,12 +2193,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>mostbet54173.help</t>
         </is>
       </c>
     </row>
@@ -1750,12 +2215,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>mostbet54319.help</t>
         </is>
       </c>
     </row>
@@ -1767,12 +2237,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>mostbet55146.online</t>
         </is>
       </c>
     </row>
@@ -1784,12 +2259,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>mostbet56053.help</t>
         </is>
       </c>
     </row>
@@ -1801,12 +2281,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>mostbet56120.help</t>
         </is>
       </c>
     </row>
@@ -1818,12 +2303,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>mostbet56890.icu</t>
         </is>
       </c>
     </row>
@@ -1835,12 +2325,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>mostbet57408.online</t>
         </is>
       </c>
     </row>
@@ -1852,12 +2347,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>mostbet61527.help</t>
         </is>
       </c>
     </row>
@@ -1869,12 +2369,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>mostbet64830.help</t>
         </is>
       </c>
     </row>
@@ -1886,12 +2391,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>mostbet65792.help</t>
         </is>
       </c>
     </row>
@@ -1903,12 +2413,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>mostbet66053.online</t>
         </is>
       </c>
     </row>
@@ -1920,12 +2435,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>mostbet66604.shop</t>
         </is>
       </c>
     </row>
@@ -1937,12 +2457,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>mostbet68204.help</t>
         </is>
       </c>
     </row>
@@ -1954,12 +2479,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>mostbet68566.icu</t>
         </is>
       </c>
     </row>
@@ -1971,12 +2501,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>mostbet68667.icu</t>
         </is>
       </c>
     </row>
@@ -1988,12 +2523,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>mostbet69416.online</t>
         </is>
       </c>
     </row>
@@ -2005,12 +2545,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>mostbet6950.help</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2567,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>mostbet69754.shop</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2589,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>mostbet7178.help</t>
         </is>
       </c>
     </row>
@@ -2056,12 +2611,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>mostbet73221.help</t>
         </is>
       </c>
     </row>
@@ -2073,12 +2633,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>mostbet73713.online</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2655,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>mostbet73936.icu</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2677,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>mostbet76914.help</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2699,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>mostbet77382.online</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2721,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>mostbet78063.help</t>
         </is>
       </c>
     </row>
@@ -2158,12 +2743,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>mostbet78071.company</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2765,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>mostbet78394.help</t>
         </is>
       </c>
     </row>
@@ -2192,12 +2787,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>mostbet80295.help</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2809,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>mostbet80738.help</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2831,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>mostbet81396.help</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2853,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>mostbet83468.icu</t>
         </is>
       </c>
     </row>
@@ -2260,12 +2875,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>mostbet84736.help</t>
         </is>
       </c>
     </row>
@@ -2277,12 +2897,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>mostbet85974.help</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2919,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>mostbet87235.help</t>
         </is>
       </c>
     </row>
@@ -2311,12 +2941,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>mostbet8828.help</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2963,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>mostbet88517.online</t>
         </is>
       </c>
     </row>
@@ -2345,12 +2985,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>mostbet90088.company</t>
         </is>
       </c>
     </row>
@@ -2362,12 +3007,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>mostbet90753.help</t>
         </is>
       </c>
     </row>
@@ -2379,12 +3029,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>mostbet93580.help</t>
         </is>
       </c>
     </row>
@@ -2396,12 +3051,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>mostbet93642.company</t>
         </is>
       </c>
     </row>
@@ -2413,12 +3073,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>mostbet95063.online</t>
         </is>
       </c>
     </row>
@@ -2430,12 +3095,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>mostbet96810.help</t>
         </is>
       </c>
     </row>
@@ -2447,12 +3117,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>mostbet97198.help</t>
         </is>
       </c>
     </row>
@@ -2464,12 +3139,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>strike-07-mono-hidden</t>
+          <t>Trademark Infringement</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Trademark Infringement</t>
+          <t>strike-07-mono-hidden</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>mostbet97812.online</t>
         </is>
       </c>
     </row>
